--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N104_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N104_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.18164876560206</v>
+        <v>5.717017924410334</v>
       </c>
       <c r="D2" t="n">
-        <v>14.97942443627969</v>
+        <v>2.434156470895449</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
